--- a/artfynd/A 8205-2026 artfynd.xlsx
+++ b/artfynd/A 8205-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -899,6 +899,297 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>133645753</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57958</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Blåsmark, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>787649</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7249402</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>133645758</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57145</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Blåsmark, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>787373</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7248915</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133646234</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79333</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Blåsmark, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>787590</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7249404</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-26</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8205-2026 artfynd.xlsx
+++ b/artfynd/A 8205-2026 artfynd.xlsx
@@ -1098,7 +1098,7 @@
         <v>133646234</v>
       </c>
       <c r="B6" t="n">
-        <v>79333</v>
+        <v>79334</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 8205-2026 artfynd.xlsx
+++ b/artfynd/A 8205-2026 artfynd.xlsx
@@ -1098,7 +1098,7 @@
         <v>133646234</v>
       </c>
       <c r="B6" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 8205-2026 artfynd.xlsx
+++ b/artfynd/A 8205-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130082212</v>
+        <v>133646234</v>
       </c>
       <c r="B2" t="n">
-        <v>58309</v>
+        <v>79373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103018</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Blåsmark, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>787557</v>
+        <v>787590</v>
       </c>
       <c r="R2" t="n">
-        <v>7249433</v>
+        <v>7249404</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:03</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:03</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,7 +757,6 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AR2" t="inlineStr"/>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -792,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133420012</v>
+        <v>133645753</v>
       </c>
       <c r="B3" t="n">
-        <v>58410</v>
+        <v>57975</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,49 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103001</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bräntberget, Nb</t>
+          <t>Blåsmark, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>787600</v>
+        <v>787649</v>
       </c>
       <c r="R3" t="n">
-        <v>7249376</v>
+        <v>7249402</v>
       </c>
       <c r="S3" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,57 +857,65 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tomas Carlsson</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tomas Carlsson</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133645753</v>
+        <v>133247526</v>
       </c>
       <c r="B4" t="n">
-        <v>57975</v>
+        <v>57162</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Blåsmark, Nb</t>
+          <t>Bräntberget, Bräntberget, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>787649</v>
+        <v>787482</v>
       </c>
       <c r="R4" t="n">
-        <v>7249402</v>
+        <v>7249102</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,12 +942,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Lämplig plats för tjäderlek?</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,19 +967,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Tomas Carlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Elin Lindmark</t>
+          <t>Tomas Carlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133645758</v>
+        <v>133645757</v>
       </c>
       <c r="B5" t="n">
         <v>57162</v>
@@ -1095,10 +1076,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133646234</v>
+        <v>133420012</v>
       </c>
       <c r="B6" t="n">
-        <v>79366</v>
+        <v>58410</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1106,37 +1087,49 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>103001</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Blåsmark, Nb</t>
+          <t>Bräntberget, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>787590</v>
+        <v>787600</v>
       </c>
       <c r="R6" t="n">
-        <v>7249404</v>
+        <v>7249376</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1160,12 +1153,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1180,26 +1173,26 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Tomas Carlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Elin Lindmark</t>
+          <t>Tomas Carlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134163768</v>
+        <v>130082212</v>
       </c>
       <c r="B7" t="n">
-        <v>58461</v>
+        <v>58439</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1225,27 +1218,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bräntberget, Nb</t>
+          <t>Blåsmark, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>787333</v>
+        <v>787557</v>
       </c>
       <c r="R7" t="n">
-        <v>7248927</v>
+        <v>7249433</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1269,12 +1259,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1286,18 +1286,128 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
+      <c r="AR7" t="inlineStr"/>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134163768</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58461</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bräntberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>787333</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7248927</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Tomas Carlsson</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Tomas Carlsson</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8205-2026 artfynd.xlsx
+++ b/artfynd/A 8205-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133645753</v>
+        <v>133275252</v>
       </c>
       <c r="B3" t="n">
         <v>57975</v>
@@ -800,17 +800,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Blåsmark, Nb</t>
+          <t>Bräntberget, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>787649</v>
+        <v>787363</v>
       </c>
       <c r="R3" t="n">
-        <v>7249402</v>
+        <v>7248899</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -837,12 +849,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Två bohål på samma gran. Ingångshål ca 45-50 mm.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -857,65 +874,57 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Tomas Carlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Elin Lindmark</t>
+          <t>Tomas Carlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133247526</v>
+        <v>133645753</v>
       </c>
       <c r="B4" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bräntberget, Bräntberget, Nb</t>
+          <t>Blåsmark, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>787482</v>
+        <v>787649</v>
       </c>
       <c r="R4" t="n">
-        <v>7249102</v>
+        <v>7249402</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -942,17 +951,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Lämplig plats för tjäderlek?</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -967,19 +971,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tomas Carlsson</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tomas Carlsson</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133645757</v>
+        <v>133247526</v>
       </c>
       <c r="B5" t="n">
         <v>57162</v>
@@ -1008,16 +1012,24 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Blåsmark, Nb</t>
+          <t>Bräntberget, Bräntberget, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>787373</v>
+        <v>787482</v>
       </c>
       <c r="R5" t="n">
-        <v>7248915</v>
+        <v>7249102</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1044,12 +1056,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Lämplig plats för tjäderlek?</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1064,72 +1081,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Tomas Carlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Elin Lindmark</t>
+          <t>Tomas Carlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133420012</v>
+        <v>133645757</v>
       </c>
       <c r="B6" t="n">
-        <v>58410</v>
+        <v>57162</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103001</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bräntberget, Nb</t>
+          <t>Blåsmark, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>787600</v>
+        <v>787373</v>
       </c>
       <c r="R6" t="n">
-        <v>7249376</v>
+        <v>7248915</v>
       </c>
       <c r="S6" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1153,12 +1158,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,44 +1178,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Tomas Carlsson</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Tomas Carlsson</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130082212</v>
+        <v>133420012</v>
       </c>
       <c r="B7" t="n">
-        <v>58439</v>
+        <v>58410</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103018</v>
+        <v>103001</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1218,24 +1223,27 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Blåsmark, Nb</t>
+          <t>Bräntberget, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>787557</v>
+        <v>787600</v>
       </c>
       <c r="R7" t="n">
-        <v>7249433</v>
+        <v>7249376</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1259,22 +1267,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:03</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:03</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1286,26 +1284,25 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AR7" t="inlineStr"/>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Tomas Carlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via Elin Lindmark</t>
+          <t>Tomas Carlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134163768</v>
+        <v>130082212</v>
       </c>
       <c r="B8" t="n">
-        <v>58461</v>
+        <v>58439</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1335,27 +1332,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bräntberget, Nb</t>
+          <t>Blåsmark, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>787333</v>
+        <v>787557</v>
       </c>
       <c r="R8" t="n">
-        <v>7248927</v>
+        <v>7249433</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1379,12 +1373,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1396,18 +1400,128 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
+      <c r="AR8" t="inlineStr"/>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>134163768</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58461</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bräntberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>787333</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7248927</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>Tomas Carlsson</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>Tomas Carlsson</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8205-2026 artfynd.xlsx
+++ b/artfynd/A 8205-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -983,32 +983,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133247526</v>
+        <v>134156084</v>
       </c>
       <c r="B5" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,7 +1016,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1026,13 +1026,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>787482</v>
+        <v>787381</v>
       </c>
       <c r="R5" t="n">
-        <v>7249102</v>
+        <v>7248892</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1056,17 +1056,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Lämplig plats för tjäderlek?</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133645757</v>
+        <v>133247526</v>
       </c>
       <c r="B6" t="n">
         <v>57162</v>
@@ -1122,16 +1117,24 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Blåsmark, Nb</t>
+          <t>Bräntberget, Bräntberget, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>787373</v>
+        <v>787482</v>
       </c>
       <c r="R6" t="n">
-        <v>7248915</v>
+        <v>7249102</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1158,12 +1161,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Lämplig plats för tjäderlek?</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1178,72 +1186,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Tomas Carlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Elin Lindmark</t>
+          <t>Tomas Carlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133420012</v>
+        <v>133645757</v>
       </c>
       <c r="B7" t="n">
-        <v>58410</v>
+        <v>57162</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103001</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bräntberget, Nb</t>
+          <t>Blåsmark, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>787600</v>
+        <v>787373</v>
       </c>
       <c r="R7" t="n">
-        <v>7249376</v>
+        <v>7248915</v>
       </c>
       <c r="S7" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1267,12 +1263,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,44 +1283,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Tomas Carlsson</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Tomas Carlsson</t>
+          <t>Via Elin Lindmark</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130082212</v>
+        <v>133420012</v>
       </c>
       <c r="B8" t="n">
-        <v>58439</v>
+        <v>58410</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103018</v>
+        <v>103001</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1332,24 +1328,27 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Blåsmark, Nb</t>
+          <t>Bräntberget, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>787557</v>
+        <v>787600</v>
       </c>
       <c r="R8" t="n">
-        <v>7249433</v>
+        <v>7249376</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1373,22 +1372,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:03</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:03</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1400,26 +1389,25 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AR8" t="inlineStr"/>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Tomas Carlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Via Elin Lindmark</t>
+          <t>Tomas Carlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134163768</v>
+        <v>130082212</v>
       </c>
       <c r="B9" t="n">
-        <v>58461</v>
+        <v>58439</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1449,27 +1437,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bräntberget, Nb</t>
+          <t>Blåsmark, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>787333</v>
+        <v>787557</v>
       </c>
       <c r="R9" t="n">
-        <v>7248927</v>
+        <v>7249433</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1493,12 +1478,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1510,18 +1505,128 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
+      <c r="AR9" t="inlineStr"/>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>134163768</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58461</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bräntberget, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>787333</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7248927</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Tomas Carlsson</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Tomas Carlsson</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8205-2026 artfynd.xlsx
+++ b/artfynd/A 8205-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133646234</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -883,6 +893,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133275252</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133645753</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1085,6 +1105,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134156084</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1195,6 +1220,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133247526</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1292,6 +1322,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133645757</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1401,6 +1436,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133420012</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1518,6 +1558,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130082212</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1627,8 +1672,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134163768</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>